--- a/artfynd/A 54381-2023 artfynd.xlsx
+++ b/artfynd/A 54381-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ18"/>
+  <dimension ref="A1:AZ19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2414,10 +2414,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>73492516</v>
+        <v>136931434</v>
       </c>
       <c r="B17" t="n">
-        <v>101228</v>
+        <v>101563</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2425,21 +2425,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>222771</v>
+        <v>222498</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2453,13 +2453,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>553192</v>
+        <v>553643</v>
       </c>
       <c r="R17" t="n">
-        <v>6557635</v>
+        <v>6557198</v>
       </c>
       <c r="S17" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2483,12 +2483,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2018-10-05</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2018-10-05</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2501,37 +2501,31 @@
       <c r="AG17" t="b">
         <v>0</v>
       </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>Grandominerad gallringsskog</t>
-        </is>
-      </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Bo Karlsson</t>
+          <t>Staffan Fridh</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Bo Karlsson</t>
-        </is>
-      </c>
-      <c r="AY17" t="inlineStr"/>
+          <t>Edith Bremer Storm</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/73492516</t>
+          <t>https://artportalen.se/Sighting/136931434</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>73492522</v>
+        <v>73492516</v>
       </c>
       <c r="B18" t="n">
         <v>101228</v>
@@ -2570,10 +2564,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>553249</v>
+        <v>553192</v>
       </c>
       <c r="R18" t="n">
-        <v>6557599</v>
+        <v>6557635</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2641,6 +2635,123 @@
       </c>
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73492516</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>73492522</v>
+      </c>
+      <c r="B19" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Kalkbrottsvillorna, Srm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>553249</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6557599</v>
+      </c>
+      <c r="S19" t="n">
+        <v>25</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Vingåker</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2018-10-05</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2018-10-05</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>Grandominerad gallringsskog</t>
+        </is>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Bo Karlsson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Bo Karlsson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/73492522</t>
         </is>
@@ -2665,6 +2776,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 54381-2023 artfynd.xlsx
+++ b/artfynd/A 54381-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ19"/>
+  <dimension ref="A1:AZ20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1829,10 +1829,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>73485197</v>
+        <v>136949509</v>
       </c>
       <c r="B12" t="n">
-        <v>101326</v>
+        <v>106406</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1840,41 +1840,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>222498</v>
+        <v>221141</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Kalkbrottsvillorna, Srm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>553300</v>
+        <v>553623</v>
       </c>
       <c r="R12" t="n">
-        <v>6557605</v>
+        <v>6557190</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1898,12 +1894,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2018-10-05</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2018-10-05</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1912,41 +1908,34 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>Grandominerad skog</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Bo Karlsson</t>
+          <t>Staffan Fridh</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Bo Karlsson</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr"/>
+          <t>Saga Samuelsson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/73485197</t>
+          <t>https://artportalen.se/Sighting/136949509</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>73486968</v>
+        <v>73485197</v>
       </c>
       <c r="B13" t="n">
         <v>101326</v>
@@ -1985,10 +1974,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>553512</v>
+        <v>553300</v>
       </c>
       <c r="R13" t="n">
-        <v>6557367</v>
+        <v>6557605</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2040,7 +2029,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Barrblandskog skog</t>
+          <t>Grandominerad skog</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2057,13 +2046,13 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/73486968</t>
+          <t>https://artportalen.se/Sighting/73485197</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>73492390</v>
+        <v>73486968</v>
       </c>
       <c r="B14" t="n">
         <v>101326</v>
@@ -2102,10 +2091,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>553475</v>
+        <v>553512</v>
       </c>
       <c r="R14" t="n">
-        <v>6557406</v>
+        <v>6557367</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2157,7 +2146,7 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>Barrblandskog,</t>
+          <t>Barrblandskog skog</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2174,13 +2163,13 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/73492390</t>
+          <t>https://artportalen.se/Sighting/73486968</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>73492404</v>
+        <v>73492390</v>
       </c>
       <c r="B15" t="n">
         <v>101326</v>
@@ -2219,10 +2208,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>553417</v>
+        <v>553475</v>
       </c>
       <c r="R15" t="n">
-        <v>6557467</v>
+        <v>6557406</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2291,13 +2280,13 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/73492404</t>
+          <t>https://artportalen.se/Sighting/73492390</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>73593983</v>
+        <v>73492404</v>
       </c>
       <c r="B16" t="n">
         <v>101326</v>
@@ -2332,14 +2321,14 @@
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Kalkbrottsvillorna mot sjön, Srm</t>
+          <t>Kalkbrottsvillorna, Srm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>552990</v>
+        <v>553417</v>
       </c>
       <c r="R16" t="n">
-        <v>6557738</v>
+        <v>6557467</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2366,12 +2355,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2018-10-14</t>
+          <t>2018-10-05</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2018-10-14</t>
+          <t>2018-10-05</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2391,7 +2380,7 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>Lövblandskog</t>
+          <t>Barrblandskog,</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2408,16 +2397,16 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/73593983</t>
+          <t>https://artportalen.se/Sighting/73492404</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>136931434</v>
+        <v>73593983</v>
       </c>
       <c r="B17" t="n">
-        <v>101563</v>
+        <v>101326</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2449,17 +2438,17 @@
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Kalkbrottsvillorna, Srm</t>
+          <t>Kalkbrottsvillorna mot sjön, Srm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>553643</v>
+        <v>552990</v>
       </c>
       <c r="R17" t="n">
-        <v>6557198</v>
+        <v>6557738</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2483,12 +2472,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2018-10-14</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2018-10-14</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2501,34 +2490,40 @@
       <c r="AG17" t="b">
         <v>0</v>
       </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>Lövblandskog</t>
+        </is>
+      </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Staffan Fridh</t>
+          <t>Bo Karlsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Edith Bremer Storm</t>
-        </is>
-      </c>
-      <c r="AY17" t="inlineStr">
-        <is>
-          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
-        </is>
-      </c>
+          <t>Bo Karlsson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136931434</t>
+          <t>https://artportalen.se/Sighting/73593983</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>73492516</v>
+        <v>136931434</v>
       </c>
       <c r="B18" t="n">
-        <v>101228</v>
+        <v>101563</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2536,21 +2531,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>222771</v>
+        <v>222498</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2564,13 +2559,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>553192</v>
+        <v>553643</v>
       </c>
       <c r="R18" t="n">
-        <v>6557635</v>
+        <v>6557198</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2594,12 +2589,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2018-10-05</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2018-10-05</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2612,37 +2607,31 @@
       <c r="AG18" t="b">
         <v>0</v>
       </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t>Grandominerad gallringsskog</t>
-        </is>
-      </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Bo Karlsson</t>
+          <t>Staffan Fridh</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Bo Karlsson</t>
-        </is>
-      </c>
-      <c r="AY18" t="inlineStr"/>
+          <t>Edith Bremer Storm</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/73492516</t>
+          <t>https://artportalen.se/Sighting/136931434</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>73492522</v>
+        <v>73492516</v>
       </c>
       <c r="B19" t="n">
         <v>101228</v>
@@ -2681,10 +2670,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>553249</v>
+        <v>553192</v>
       </c>
       <c r="R19" t="n">
-        <v>6557599</v>
+        <v>6557635</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2752,6 +2741,123 @@
       </c>
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73492516</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>73492522</v>
+      </c>
+      <c r="B20" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Kalkbrottsvillorna, Srm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>553249</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6557599</v>
+      </c>
+      <c r="S20" t="n">
+        <v>25</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Vingåker</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2018-10-05</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2018-10-05</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>Grandominerad gallringsskog</t>
+        </is>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Bo Karlsson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Bo Karlsson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/73492522</t>
         </is>
@@ -2777,6 +2883,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 54381-2023 artfynd.xlsx
+++ b/artfynd/A 54381-2023 artfynd.xlsx
@@ -1832,7 +1832,7 @@
         <v>136949509</v>
       </c>
       <c r="B12" t="n">
-        <v>106406</v>
+        <v>106412</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2523,7 +2523,7 @@
         <v>136931434</v>
       </c>
       <c r="B18" t="n">
-        <v>101563</v>
+        <v>101569</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 54381-2023 artfynd.xlsx
+++ b/artfynd/A 54381-2023 artfynd.xlsx
@@ -1832,7 +1832,7 @@
         <v>136949509</v>
       </c>
       <c r="B12" t="n">
-        <v>106412</v>
+        <v>106414</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2523,7 +2523,7 @@
         <v>136931434</v>
       </c>
       <c r="B18" t="n">
-        <v>101569</v>
+        <v>101571</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 54381-2023 artfynd.xlsx
+++ b/artfynd/A 54381-2023 artfynd.xlsx
@@ -1832,7 +1832,7 @@
         <v>136949509</v>
       </c>
       <c r="B12" t="n">
-        <v>106414</v>
+        <v>106415</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2523,7 +2523,7 @@
         <v>136931434</v>
       </c>
       <c r="B18" t="n">
-        <v>101571</v>
+        <v>101572</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 54381-2023 artfynd.xlsx
+++ b/artfynd/A 54381-2023 artfynd.xlsx
@@ -1832,7 +1832,7 @@
         <v>136949509</v>
       </c>
       <c r="B12" t="n">
-        <v>106415</v>
+        <v>106421</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2523,7 +2523,7 @@
         <v>136931434</v>
       </c>
       <c r="B18" t="n">
-        <v>101572</v>
+        <v>101578</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 54381-2023 artfynd.xlsx
+++ b/artfynd/A 54381-2023 artfynd.xlsx
@@ -1832,7 +1832,7 @@
         <v>136949509</v>
       </c>
       <c r="B12" t="n">
-        <v>106421</v>
+        <v>106425</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2523,7 +2523,7 @@
         <v>136931434</v>
       </c>
       <c r="B18" t="n">
-        <v>101578</v>
+        <v>101582</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 54381-2023 artfynd.xlsx
+++ b/artfynd/A 54381-2023 artfynd.xlsx
@@ -1832,7 +1832,7 @@
         <v>136949509</v>
       </c>
       <c r="B12" t="n">
-        <v>106425</v>
+        <v>106427</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2523,7 +2523,7 @@
         <v>136931434</v>
       </c>
       <c r="B18" t="n">
-        <v>101582</v>
+        <v>101584</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 54381-2023 artfynd.xlsx
+++ b/artfynd/A 54381-2023 artfynd.xlsx
@@ -1832,7 +1832,7 @@
         <v>136949509</v>
       </c>
       <c r="B12" t="n">
-        <v>106427</v>
+        <v>106429</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2523,7 +2523,7 @@
         <v>136931434</v>
       </c>
       <c r="B18" t="n">
-        <v>101584</v>
+        <v>101586</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 54381-2023 artfynd.xlsx
+++ b/artfynd/A 54381-2023 artfynd.xlsx
@@ -1832,7 +1832,7 @@
         <v>136949509</v>
       </c>
       <c r="B12" t="n">
-        <v>106429</v>
+        <v>106442</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2523,7 +2523,7 @@
         <v>136931434</v>
       </c>
       <c r="B18" t="n">
-        <v>101586</v>
+        <v>101599</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 54381-2023 artfynd.xlsx
+++ b/artfynd/A 54381-2023 artfynd.xlsx
@@ -1832,7 +1832,7 @@
         <v>136949509</v>
       </c>
       <c r="B12" t="n">
-        <v>106442</v>
+        <v>106444</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2523,7 +2523,7 @@
         <v>136931434</v>
       </c>
       <c r="B18" t="n">
-        <v>101599</v>
+        <v>101601</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 54381-2023 artfynd.xlsx
+++ b/artfynd/A 54381-2023 artfynd.xlsx
@@ -1832,7 +1832,7 @@
         <v>136949509</v>
       </c>
       <c r="B12" t="n">
-        <v>106444</v>
+        <v>106448</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2523,7 +2523,7 @@
         <v>136931434</v>
       </c>
       <c r="B18" t="n">
-        <v>101601</v>
+        <v>101604</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 54381-2023 artfynd.xlsx
+++ b/artfynd/A 54381-2023 artfynd.xlsx
@@ -1832,7 +1832,7 @@
         <v>136949509</v>
       </c>
       <c r="B12" t="n">
-        <v>106448</v>
+        <v>106467</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2523,7 +2523,7 @@
         <v>136931434</v>
       </c>
       <c r="B18" t="n">
-        <v>101604</v>
+        <v>101619</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 54381-2023 artfynd.xlsx
+++ b/artfynd/A 54381-2023 artfynd.xlsx
@@ -1832,7 +1832,7 @@
         <v>136949509</v>
       </c>
       <c r="B12" t="n">
-        <v>106467</v>
+        <v>106468</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2523,7 +2523,7 @@
         <v>136931434</v>
       </c>
       <c r="B18" t="n">
-        <v>101619</v>
+        <v>101620</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 54381-2023 artfynd.xlsx
+++ b/artfynd/A 54381-2023 artfynd.xlsx
@@ -1832,7 +1832,7 @@
         <v>136949509</v>
       </c>
       <c r="B12" t="n">
-        <v>106468</v>
+        <v>106473</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2523,7 +2523,7 @@
         <v>136931434</v>
       </c>
       <c r="B18" t="n">
-        <v>101620</v>
+        <v>101625</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 54381-2023 artfynd.xlsx
+++ b/artfynd/A 54381-2023 artfynd.xlsx
@@ -1832,7 +1832,7 @@
         <v>136949509</v>
       </c>
       <c r="B12" t="n">
-        <v>106473</v>
+        <v>106476</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2523,7 +2523,7 @@
         <v>136931434</v>
       </c>
       <c r="B18" t="n">
-        <v>101625</v>
+        <v>101628</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 54381-2023 artfynd.xlsx
+++ b/artfynd/A 54381-2023 artfynd.xlsx
@@ -1832,7 +1832,7 @@
         <v>136949509</v>
       </c>
       <c r="B12" t="n">
-        <v>106476</v>
+        <v>106482</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2523,7 +2523,7 @@
         <v>136931434</v>
       </c>
       <c r="B18" t="n">
-        <v>101628</v>
+        <v>101634</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 54381-2023 artfynd.xlsx
+++ b/artfynd/A 54381-2023 artfynd.xlsx
@@ -1832,7 +1832,7 @@
         <v>136949509</v>
       </c>
       <c r="B12" t="n">
-        <v>106482</v>
+        <v>106483</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 54381-2023 artfynd.xlsx
+++ b/artfynd/A 54381-2023 artfynd.xlsx
@@ -1832,7 +1832,7 @@
         <v>136949509</v>
       </c>
       <c r="B12" t="n">
-        <v>106483</v>
+        <v>106495</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2523,7 +2523,7 @@
         <v>136931434</v>
       </c>
       <c r="B18" t="n">
-        <v>101634</v>
+        <v>101646</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 54381-2023 artfynd.xlsx
+++ b/artfynd/A 54381-2023 artfynd.xlsx
@@ -1832,7 +1832,7 @@
         <v>136949509</v>
       </c>
       <c r="B12" t="n">
-        <v>106495</v>
+        <v>106496</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2523,7 +2523,7 @@
         <v>136931434</v>
       </c>
       <c r="B18" t="n">
-        <v>101646</v>
+        <v>101647</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 54381-2023 artfynd.xlsx
+++ b/artfynd/A 54381-2023 artfynd.xlsx
@@ -1832,7 +1832,7 @@
         <v>136949509</v>
       </c>
       <c r="B12" t="n">
-        <v>106496</v>
+        <v>106499</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2523,7 +2523,7 @@
         <v>136931434</v>
       </c>
       <c r="B18" t="n">
-        <v>101647</v>
+        <v>101650</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 54381-2023 artfynd.xlsx
+++ b/artfynd/A 54381-2023 artfynd.xlsx
@@ -1832,7 +1832,7 @@
         <v>136949509</v>
       </c>
       <c r="B12" t="n">
-        <v>106499</v>
+        <v>106501</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2523,7 +2523,7 @@
         <v>136931434</v>
       </c>
       <c r="B18" t="n">
-        <v>101650</v>
+        <v>101651</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 54381-2023 artfynd.xlsx
+++ b/artfynd/A 54381-2023 artfynd.xlsx
@@ -1832,7 +1832,7 @@
         <v>136949509</v>
       </c>
       <c r="B12" t="n">
-        <v>106501</v>
+        <v>106505</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2523,7 +2523,7 @@
         <v>136931434</v>
       </c>
       <c r="B18" t="n">
-        <v>101651</v>
+        <v>101654</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
